--- a/docs/review/Gardenly-atvilagitas.xlsx
+++ b/docs/review/Gardenly-atvilagitas.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="90">
   <si>
     <t xml:space="preserve">Gardenly – átvilágítás: felhasználói élmény, biztonság, szerzői jog</t>
   </si>
@@ -66,42 +66,63 @@
     <t xml:space="preserve">Tartós tárhely kérése a böngészőtől, és figyelmeztetés, ha ezt nem kapja meg. Mentés-emlékeztető (pl. hetente vagy nagyobb módosítás után). Egy kattintásos „mentés fájlba”.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kész</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tartós tárhely kérése, mentési állapot, heti emlékeztető, mentés fájlba (0.3.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jogi szempont</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A „nem mérgező” és „tüske nélkül” szűrők biztonságérzetet adnak (gyerek, kutya, macska), pedig az adatok egy része „ellenőrizendő”.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jól látható felelősségkizárás a szűrőnél és az infókártyán: tájékoztató adat, mérgező növénynél kérdezz szakembert. Az adatforrások megnevezése.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figyelmeztetés a szűrőnél, infókártyán, terület korlátjánál; adatforrások a Jogi információkban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A kód nagy részét MI írta. Az EU-s és a magyar szerzői jogban a védelemhez emberi alkotás kell, így a „minden jog fenntartva” hatóköre a kódra bizonytalan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jogászi egyeztetés. A saját alkotói rész dokumentálása (specifikáció, döntések, arculat, növényadatok). Védelem felhasználási feltételekkel és védjeggyel is.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nyitott</t>
   </si>
   <si>
-    <t xml:space="preserve">Jogi szempont</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A „nem mérgező” és „tüske nélkül” szűrők biztonságérzetet adnak (gyerek, kutya, macska), pedig az adatok egy része „ellenőrizendő”.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jól látható felelősségkizárás a szűrőnél és az infókártyán: tájékoztató adat, mérgező növénynél kérdezz szakembert. Az adatforrások megnevezése.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A kód nagy részét MI írta. Az EU-s és a magyar szerzői jogban a védelemhez emberi alkotás kell, így a „minden jog fenntartva” hatóköre a kódra bizonytalan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jogászi egyeztetés. A saját alkotói rész dokumentálása (specifikáció, döntések, arculat, növényadatok). Védelem felhasználási feltételekkel és védjeggyel is.</t>
-  </si>
-  <si>
     <t xml:space="preserve">A felhasznált nyílt forrású összetevők licencei kötelezően mellékelendők, és ezt a „minden jog fenntartva” nem írhatja felül. Ilyenek: React, Zustand, fflate, Workbox (MIT); idb-keyval (Apache-2.0); a három betűtípus (SIL OFL).</t>
   </si>
   <si>
     <t xml:space="preserve">Harmadik féltől származó licencek listájának automatikus generálása buildkor, link a Névjegyben.</t>
   </si>
   <si>
+    <t xml:space="preserve">public/third-party-licenses.txt buildkor generálva, link a Névjegyben</t>
+  </si>
+  <si>
     <t xml:space="preserve">A Wikipédia/Commons fotók általában CC BY-SA licencűek. Ehhez szerző, licencnév, licenclink és forráslink kell, az infókártyán viszont csak a szerző és a licenc neve látszik.</t>
   </si>
   <si>
     <t xml:space="preserve">Licenc- és forráslink a fotó alá. Ha a fotó exportba kerül, ott is feltüntetni.</t>
   </si>
   <si>
+    <t xml:space="preserve">Licenc- és Commons-forráslink az infókártyán és a növényűrlapon</t>
+  </si>
+  <si>
     <t xml:space="preserve">A „Gardenly” névre nem volt védjegykutatás. Lehet azonos nevű kertészeti alkalmazás vagy cég.</t>
   </si>
   <si>
     <t xml:space="preserve">Kutatás az EUIPO, az SZTNH és az app store-ok adatbázisában még a nyilvános megjelenés előtt. Szükség esetén bejelentés.</t>
   </si>
   <si>
+    <t xml:space="preserve">Folyamatban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Előzetes kutatás: docs/legal/NEVKUTATAS.md – több azonos nevű app és egy USA védjegy; hivatalos kutatás és döntés hátravan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Felhasználói élmény</t>
   </si>
   <si>
@@ -123,30 +144,45 @@
     <t xml:space="preserve">Az ilyen cellák elé aposztróf.</t>
   </si>
   <si>
+    <t xml:space="preserve">Aposztróf a képletjellel kezdődő cellák elé (CSV, táblázat másolás), importnál visszaáll</t>
+  </si>
+  <si>
     <t xml:space="preserve">A mentés és a megosztott link betöltése csak néhány mezőt ellenőriz. Egy hibás vagy szándékosan torzított fájl összeomlaszthatja az alkalmazást. Mivel automatikusan mentődik, indításkor újra összeomolhat.</t>
   </si>
   <si>
     <t xml:space="preserve">Teljes sémaellenőrzés és méretkorlát. Hibakezelő képernyő „Mentés letöltése / Alaphelyzet” lehetőséggel.</t>
   </si>
   <si>
+    <t xml:space="preserve">Teljes szerkezeti ellenőrzés és méretkorlát; „Valami elromlott” helyreállító képernyő</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nincs CSP (tartalombiztonsági szabály).</t>
   </si>
   <si>
     <t xml:space="preserve">CSP meta-tag: csak a saját fájlok, data/blob képek és a Wikimedia-címek engedélyezve.</t>
   </si>
   <si>
+    <t xml:space="preserve">CSP meta-tag a buildben, e2e teszt sértés nélkül</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nyilvános közzétételnél adatvédelmi tájékoztató kell. Az alkalmazás kérést küld a Wikimédiának (IP-cím, latin nevek), a megosztott link a teljes tervet tartalmazza, a ChatGPT-küldésnél a felhasználó továbbítja az adatokat.</t>
   </si>
   <si>
     <t xml:space="preserve">Rövid adatvédelmi tájékoztató az alkalmazásban és a README-ben.</t>
   </si>
   <si>
+    <t xml:space="preserve">Adatvédelmi tájékoztató (HU/EN) az alkalmazásban és docs/legal alatt – jogászi átnézés javasolt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nincsenek felhasználási feltételek (felelősségkorlátozás, MI-képek, árak és adatok pontossága).</t>
   </si>
   <si>
     <t xml:space="preserve">Rövid felhasználási feltételek a Névjegyben.</t>
   </si>
   <si>
+    <t xml:space="preserve">Felhasználási feltételek (HU/EN) – jogászi átnézés javasolt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ha a GitHub-tároló nyilvános, a GitHub feltételei szerint mások megnézhetik és forkolhatják, függetlenül a LICENSE fájltól.</t>
   </si>
   <si>
@@ -165,12 +201,18 @@
     <t xml:space="preserve">Helyszín vagy klímazóna beállítás a projektben.</t>
   </si>
   <si>
+    <t xml:space="preserve">Helyszín és éghajlat beállítás (városok vagy saját fagydátumok)</t>
+  </si>
+  <si>
     <t xml:space="preserve">A növényadatok egy része „ellenőrizendő”.</t>
   </si>
   <si>
     <t xml:space="preserve">Szakértői átnézés, forrás és dátum mezőnként.</t>
   </si>
   <si>
+    <t xml:space="preserve">Eszközök kész: adatforrás, ellenőrzés dátuma, „Ellenőrizendők listája (CSV)”; maga a szakértői átnézés hátravan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Valódi eszközön nem volt teszt: iPhone/Android megosztó menü a ChatGPT felé, 200+ tő gördülékenysége.</t>
   </si>
   <si>
@@ -187,6 +229,9 @@
   </si>
   <si>
     <t xml:space="preserve">„Gyors műveletek” gomb vagy kereshető parancslista. Kezdő ellenőrzőlista az első tervhez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚡ Gyors műveletek (Ctrl+K) és „Az első terv lépései” ellenőrzőlista</t>
   </si>
   <si>
     <t xml:space="preserve">A látványképek és háttérfotók nagy mentéseket okoznak, a tárhelykvóta betelhet.</t>
@@ -412,16 +457,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -441,7 +490,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -449,7 +498,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -457,7 +506,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -465,7 +514,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -478,7 +527,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -490,6 +539,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF808080"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -820,625 +877,651 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="G5" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="C18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="B20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="G23" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="B24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="B26" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="B27" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="B28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="B29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="B30" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+      <c r="B31" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="n">
+      <c r="C31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="6"/>
+      <c r="G31" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G31"/>
@@ -1447,18 +1530,18 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C31">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$C5="High"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$C5="Normal"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$C5="Low"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:G31">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$F5="Kész"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1487,163 +1570,163 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="C3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A4,Javaslatok!$C$5:$C$31,B$3)</f>
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A4,Javaslatok!$C$5:$C$31,C$3)</f>
         <v>5</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A4,Javaslatok!$C$5:$C$31,D$3)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <f aca="false">SUM(B4:D4)</f>
         <v>7</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A4,Javaslatok!$F$5:$F$31,"Kész")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A5,Javaslatok!$C$5:$C$31,B$3)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A5,Javaslatok!$C$5:$C$31,C$3)</f>
         <v>3</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A5,Javaslatok!$C$5:$C$31,D$3)</f>
         <v>1</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="11" t="n">
         <f aca="false">SUM(B5:D5)</f>
         <v>5</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A5,Javaslatok!$F$5:$F$31,"Kész")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A6,Javaslatok!$C$5:$C$31,B$3)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A6,Javaslatok!$C$5:$C$31,C$3)</f>
         <v>3</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A6,Javaslatok!$C$5:$C$31,D$3)</f>
         <v>2</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <f aca="false">SUM(B6:D6)</f>
         <v>5</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A6,Javaslatok!$F$5:$F$31,"Kész")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A7,Javaslatok!$C$5:$C$31,B$3)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A7,Javaslatok!$C$5:$C$31,C$3)</f>
         <v>4</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A7,Javaslatok!$C$5:$C$31,D$3)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="11" t="n">
         <f aca="false">SUM(B7:D7)</f>
         <v>10</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="11" t="n">
         <f aca="false">COUNTIFS(Javaslatok!$B$5:$B$31,$A7,Javaslatok!$F$5:$F$31,"Kész")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="13" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="13" t="n">
         <f aca="false">SUM(C4:C7)</f>
         <v>15</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="13" t="n">
         <f aca="false">SUM(D4:D7)</f>
         <v>5</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <f aca="false">SUM(E4:E7)</f>
         <v>27</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="13" t="n">
         <f aca="false">SUM(F4:F7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>74</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
